--- a/artfynd/A 32937-2025 artfynd.xlsx
+++ b/artfynd/A 32937-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>126590323</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126590322</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32937-2025 artfynd.xlsx
+++ b/artfynd/A 32937-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>126590323</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126590322</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32937-2025 artfynd.xlsx
+++ b/artfynd/A 32937-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590320</v>
       </c>
       <c r="B2" t="n">
-        <v>57817</v>
+        <v>57876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,14 +776,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>126590323</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,14 +877,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>126590322</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,14 +978,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>126590321</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1087,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32937-2025 artfynd.xlsx
+++ b/artfynd/A 32937-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590320</v>
       </c>
       <c r="B2" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>126590323</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126590322</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126590321</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32937-2025 artfynd.xlsx
+++ b/artfynd/A 32937-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590320</v>
       </c>
       <c r="B2" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>126590323</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126590322</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126590321</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32937-2025 artfynd.xlsx
+++ b/artfynd/A 32937-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>126590323</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126590322</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32937-2025 artfynd.xlsx
+++ b/artfynd/A 32937-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590320</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>126590323</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126590322</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126590321</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32937-2025 artfynd.xlsx
+++ b/artfynd/A 32937-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590320</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>126590323</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126590322</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126590321</v>
       </c>
       <c r="B5" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32937-2025 artfynd.xlsx
+++ b/artfynd/A 32937-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>126590323</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126590322</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32937-2025 artfynd.xlsx
+++ b/artfynd/A 32937-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>126590323</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126590322</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
